--- a/examples/demo_data/2026客户跟进记录.xlsx
+++ b/examples/demo_data/2026客户跟进记录.xlsx
@@ -447,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>恒信地产</t>
+          <t>示例地产A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13811110001</t>
+          <t>13800000001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -474,7 +474,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>绿叶餐饮连锁</t>
+          <t>示例餐饮A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -489,7 +489,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13811110002</t>
+          <t>13800000002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -501,7 +501,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>博学教育</t>
+          <t>示例教育A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>瑞康医疗</t>
+          <t>示例医疗A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13811110004</t>
+          <t>13800000004</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>新锐传媒</t>
+          <t>示例传媒A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13811110005</t>
+          <t>13800000005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>恒信地产</t>
+          <t>示例地产A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>绿叶餐饮连锁</t>
+          <t>示例餐饮A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>恒信地产</t>
+          <t>示例地产A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>瑞康医疗</t>
+          <t>示例医疗A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新锐传媒</t>
+          <t>示例传媒A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
